--- a/02_DIA_inicio_2026_analisis_assets/rbd_9614_escuela-basica-karelmapu_nt1_nucleos.xlsx
+++ b/02_DIA_inicio_2026_analisis_assets/rbd_9614_escuela-basica-karelmapu_nt1_nucleos.xlsx
@@ -775,13 +775,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0C494E24-D4B5-45B6-8E77-5179BBEBD1E3}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9DD6EBB4-2A30-4184-9F4C-B459565D6744}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2BDD1F60-3256-4630-B526-24213BD39878}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{03F7970F-6490-40A7-80ED-9B40D7AF6D08}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{983A07F7-87BD-41A3-BF9C-333F497C81F5}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F1B6716E-A421-4EE0-B638-1972383DF6A9}"/>
 </file>